--- a/ford_recalls_input.xlsx
+++ b/ford_recalls_input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\leadgeneration\ford_recall\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F3F505-FEDA-4472-9E23-EBE682A2EBBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290FC875-A0DE-4F24-BE89-FDA7D554F3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>VIN</t>
   </si>
@@ -139,6 +139,12 @@
   </si>
   <si>
     <t>1FT7W2BTXSED96735</t>
+  </si>
+  <si>
+    <t>Account</t>
+  </si>
+  <si>
+    <t>FortierFord</t>
   </si>
 </sst>
 </file>
@@ -462,85 +468,94 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
